--- a/task202/golden/relief_referral_ceilings_2027-28.xlsx
+++ b/task202/golden/relief_referral_ceilings_2027-28.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Clause 9 ceiling at the reference household size: PHP 7,800</t>
+          <t>Clause 9 ceiling at the reference household size: PHP 8,000</t>
         </is>
       </c>
     </row>
@@ -554,13 +554,13 @@
         <v>0.5</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -578,13 +578,13 @@
         <v>0.707</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="9">
@@ -602,13 +602,13 @@
         <v>0.866</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>21.9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -626,13 +626,13 @@
         <v>1</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="11">
@@ -650,13 +650,13 @@
         <v>1.118</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="12">
@@ -674,13 +674,13 @@
         <v>1.225</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>9600</v>
+        <v>9800</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="13">
@@ -691,10 +691,10 @@
       </c>
       <c r="D13" s="13" t="inlineStr"/>
       <c r="E13" s="14" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
     </row>
   </sheetData>
@@ -730,7 +730,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lowest multiple of PHP 100 referring at or below 6.0 per cent of the scheme's awards</t>
+          <t>lowest amount in Schedule E referring at or below 6.0 per cent of the scheme's awards</t>
         </is>
       </c>
     </row>
@@ -799,21 +799,21 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Referred share at PHP 7,800</t>
+          <t>Referred share at PHP 8,000</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>5.94</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Referred share at PHP 7,700</t>
+          <t>Referred share at PHP 7,000</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>6.04</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="12">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2928</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="13">

--- a/task202/golden/relief_referral_ceilings_2027-28.xlsx
+++ b/task202/golden/relief_referral_ceilings_2027-28.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lowest amount in Schedule E referring at or below 6.0 per cent of the scheme's awards</t>
+          <t>lowest whole multiple of one thousand pesos referring at or below 6.0 per cent of the scheme's awards</t>
         </is>
       </c>
     </row>
